--- a/数据源/nouns_triplets.xlsx
+++ b/数据源/nouns_triplets.xlsx
@@ -1450,6 +1450,9 @@
   <sheetPr/>
   <dimension ref="A1:H61"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="6" max="6" width="5.88888888888889" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
